--- a/paper_table3_edgecases.xlsx
+++ b/paper_table3_edgecases.xlsx
@@ -25,43 +25,43 @@
     <t xml:space="preserve">Analysis</t>
   </si>
   <si>
-    <t xml:space="preserve">Missing Target Columns</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Both approaches handle this case equivalently.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Empty/Blank Values</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rule-based regex sufficient; LLM adds no gain here.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Inconsistent Date Formats</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Currency Formatting (Rp / thousand-sep / decimal comma)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Non-Standard Status Vocabulary</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Duplicate / Ambiguous Headers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Whitespace &amp; Inconsistent Casing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Merged Composite Fields (name+phone, product+kWh)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cross-Platform Schema Variation (EN/abbrev headers)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Schema Homonymy (real data: "Nominal"=text desc vs "Harga"=numeric amount)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rule-based homonym-priority pattern (Harga-before-Nominal) closes most of the gap on this fixture set.</t>
+    <t xml:space="preserve">EC01: Missing columns</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Both perfect</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EC02: Empty Value</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EC03: Inconsistent Dates</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EC04: Currency Formatting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EC05: Non Standard Status</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EC06: Duplicate Headers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rule-based superior</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EC07: Whitespace Casing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EC08: Merged Fields</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EC09: Platform Schema Variation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Schema Homonymy (real data)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rule-based closes gap</t>
   </si>
 </sst>
 </file>
@@ -349,15 +349,15 @@
         <v>97.3</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B4" s="3">
-        <v>99.0</v>
+        <v>99.01</v>
       </c>
       <c r="C4" s="3">
         <v>100.0</v>
@@ -368,7 +368,7 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B5" s="3">
         <v>100.0</v>
@@ -382,7 +382,7 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B6" s="3">
         <v>100.0</v>
@@ -391,21 +391,21 @@
         <v>96.0</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7" s="3">
+        <v>94.12</v>
+      </c>
+      <c r="C7" s="3">
+        <v>57.14</v>
+      </c>
+      <c r="D7" s="2" t="s">
         <v>11</v>
-      </c>
-      <c r="B7" s="3">
-        <v>94.1</v>
-      </c>
-      <c r="C7" s="3">
-        <v>53.3</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>7</v>
       </c>
     </row>
     <row r="8">
@@ -430,10 +430,10 @@
         <v>100.0</v>
       </c>
       <c r="C9" s="3">
-        <v>95.5</v>
+        <v>95.45</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10">
@@ -444,10 +444,10 @@
         <v>100.0</v>
       </c>
       <c r="C10" s="3">
-        <v>91.5</v>
+        <v>91.49</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="11">
